--- a/client/public/templates/Events_Template.xlsx
+++ b/client/public/templates/Events_Template.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Events_Template" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t xml:space="preserve">Event Title</t>
   </si>
@@ -37,6 +37,9 @@
     <t xml:space="preserve">Event Type</t>
   </si>
   <si>
+    <t xml:space="preserve">Group (TBI/NS)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Opponent (if applicable)</t>
   </si>
   <si>
@@ -55,6 +58,9 @@
     <t xml:space="preserve">Tournament</t>
   </si>
   <si>
+    <t xml:space="preserve">ALL</t>
+  </si>
+  <si>
     <t xml:space="preserve">This is an example tournament</t>
   </si>
   <si>
@@ -70,7 +76,19 @@
     <t xml:space="preserve">Practice</t>
   </si>
   <si>
+    <t xml:space="preserve">TBI</t>
+  </si>
+  <si>
     <t xml:space="preserve">This is an Example of a practice event</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice Older</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5:30-6:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NS</t>
   </si>
 </sst>
 </file>
@@ -277,8 +295,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32.73"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -302,45 +330,77 @@
       <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="0" t="s">
         <v>11</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>46286</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="0" t="s">
         <v>16</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/templates/Events_Template.xlsx
+++ b/client/public/templates/Events_Template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t xml:space="preserve">Event Title</t>
   </si>
@@ -28,7 +28,10 @@
     <t xml:space="preserve">Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Time</t>
+    <t xml:space="preserve">Start Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End Time</t>
   </si>
   <si>
     <t xml:space="preserve">Location/Venue</t>
@@ -49,6 +52,9 @@
     <t xml:space="preserve">Tournament A</t>
   </si>
   <si>
+    <t xml:space="preserve">09/09/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">All Day</t>
   </si>
   <si>
@@ -67,7 +73,13 @@
     <t xml:space="preserve">Practice Young</t>
   </si>
   <si>
-    <t xml:space="preserve">4:15-5:15</t>
+    <t xml:space="preserve">09/21/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:15 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5:15 PM</t>
   </si>
   <si>
     <t xml:space="preserve">Cary Grove High School</t>
@@ -85,7 +97,10 @@
     <t xml:space="preserve">Practice Older</t>
   </si>
   <si>
-    <t xml:space="preserve">5:30-6:45</t>
+    <t xml:space="preserve">5:30 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6:45 PM</t>
   </si>
   <si>
     <t xml:space="preserve">NS</t>
@@ -97,7 +112,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -168,7 +183,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -295,17 +310,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="21.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="32.73"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -333,74 +349,83 @@
       <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>46274</v>
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="0" t="s">
         <v>13</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="0" t="s">
         <v>16</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="E3" s="0" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="C4" s="0" t="s">
+      <c r="F4" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>19</v>
+      <c r="G4" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
